--- a/_to_delete/приложение по застройщику/Приложение 1 - GORN DEVELOPMENT.xlsx
+++ b/_to_delete/приложение по застройщику/Приложение 1 - GORN DEVELOPMENT.xlsx
@@ -1,117 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\hq.corp.mos.ru\ext\MSSR\УАСГД\26 Передача ключей\письмо\приложение по застройщику\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37188008-59D2-4C8A-9B05-2313A540592B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24330" windowHeight="11910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="24330" windowHeight="11910" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Приложение 2 Сроки передачи ключей</t>
-  </si>
-  <si>
-    <t>Наименование группы компаний</t>
-  </si>
-  <si>
-    <t>Наименование застройщика</t>
-  </si>
-  <si>
-    <t>Наименование объекта</t>
-  </si>
-  <si>
-    <t>Адрес</t>
-  </si>
-  <si>
-    <t>№ проектной декларации</t>
-  </si>
-  <si>
-    <t>Количество заключенных ДДУ, ед.</t>
-  </si>
-  <si>
-    <t>Количество исполенных ДДУ, ед.</t>
-  </si>
-  <si>
-    <t>Первоначальная дата передачи объекта долевого строительства согласно первой проекутной декаларции</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Текущая дата передачи объекта долевого строительства </t>
-  </si>
-  <si>
-    <t>Количество ДДУ 
-с переносом срока, ед.</t>
-  </si>
-  <si>
-    <t>из них:</t>
-  </si>
-  <si>
-    <t>Заключено ДС к ДДУ</t>
-  </si>
-  <si>
-    <t>не заключено ДС к ДДУ</t>
-  </si>
-  <si>
-    <t>количество ДС к ДДУ, ед.</t>
-  </si>
-  <si>
-    <t>дата передачи согласно ДС</t>
-  </si>
-  <si>
-    <t>СЗ 5 ДОНСКОЙ</t>
-  </si>
-  <si>
-    <t>Файв Тауэрс</t>
-  </si>
-  <si>
-    <t>77-001871</t>
-  </si>
-  <si>
-    <t>GORN DEVELOPMENT</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <charset val="204"/>
+      <family val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -182,44 +111,154 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -485,149 +524,191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:O6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" customWidth="1"/>
-    <col min="10" max="10" width="31" customWidth="1"/>
-    <col min="11" max="11" width="22.85546875" customWidth="1"/>
-    <col min="12" max="12" width="26.140625" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" customWidth="1"/>
-    <col min="14" max="14" width="25.42578125" customWidth="1"/>
-    <col min="15" max="15" width="22.85546875" customWidth="1"/>
+    <col width="24.5703125" customWidth="1" min="2" max="2"/>
+    <col width="21.140625" customWidth="1" min="3" max="3"/>
+    <col width="18.85546875" customWidth="1" min="4" max="4"/>
+    <col width="16.7109375" customWidth="1" min="5" max="5"/>
+    <col width="22.85546875" customWidth="1" min="6" max="6"/>
+    <col width="22.85546875" customWidth="1" min="7" max="7"/>
+    <col width="21.5703125" customWidth="1" min="8" max="8"/>
+    <col width="29.42578125" customWidth="1" min="9" max="9"/>
+    <col width="31" customWidth="1" min="10" max="10"/>
+    <col width="22.85546875" customWidth="1" min="11" max="11"/>
+    <col width="26.140625" customWidth="1" min="12" max="12"/>
+    <col width="20.85546875" customWidth="1" min="13" max="13"/>
+    <col width="25.42578125" customWidth="1" min="14" max="14"/>
+    <col width="22.85546875" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Приложение 2 Сроки передачи ключей</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="8"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Наименование группы компаний</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Наименование застройщика</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Наименование объекта</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Адрес</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>id (по данным ЕИСЖС)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>№ проектной декларации</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Количество заключенных ДДУ, ед.</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Количество исполенных ДДУ, ед.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Первоначальная дата передачи объекта долевого строительства согласно первой проекутной декаларции</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Текущая дата передачи объекта долевого строительства </t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Количество ДДУ 
+с переносом срока, ед.</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
     </row>
-    <row r="4" spans="2:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="5" t="s">
-        <v>13</v>
+    <row r="4" ht="32.25" customHeight="1">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="12" t="n"/>
+      <c r="N4" s="8" t="n"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>не заключено ДС к ДДУ</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="7"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>количество ДС к ДДУ, ед.</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="7" t="n"/>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>GORN DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>СЗ 5 ДОНСКОЙ</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Файв Тауэрс</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>32274</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>77-001871</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="n"/>
+      <c r="N6" s="1" t="n"/>
+      <c r="O6" s="1" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:I5"/>
-    <mergeCell ref="H3:H5"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="L3:N3"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="G3:G5"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="D3:D5"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:N3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="46" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="46" fitToHeight="0"/>
 </worksheet>
 </file>
--- a/_to_delete/приложение по застройщику/Приложение 1 - GORN DEVELOPMENT.xlsx
+++ b/_to_delete/приложение по застройщику/Приложение 1 - GORN DEVELOPMENT.xlsx
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -186,6 +186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -536,22 +537,22 @@
     <col width="21.140625" customWidth="1" min="3" max="3"/>
     <col width="18.85546875" customWidth="1" min="4" max="4"/>
     <col width="16.7109375" customWidth="1" min="5" max="5"/>
-    <col width="22.85546875" customWidth="1" min="6" max="6"/>
-    <col width="22.85546875" customWidth="1" min="7" max="7"/>
-    <col width="21.5703125" customWidth="1" min="8" max="8"/>
-    <col width="29.42578125" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
-    <col width="22.85546875" customWidth="1" min="11" max="11"/>
-    <col width="26.140625" customWidth="1" min="12" max="12"/>
-    <col width="20.85546875" customWidth="1" min="13" max="13"/>
-    <col width="25.42578125" customWidth="1" min="14" max="14"/>
-    <col width="22.85546875" customWidth="1" min="15" max="15"/>
+    <col width="16.5703125" customWidth="1" min="6" max="6"/>
+    <col width="16.5703125" customWidth="1" min="7" max="7"/>
+    <col width="22.85546875" customWidth="1" min="8" max="8"/>
+    <col width="21.5703125" customWidth="1" min="9" max="9"/>
+    <col width="29.42578125" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="22.85546875" customWidth="1" min="12" max="12"/>
+    <col width="26.140625" customWidth="1" min="13" max="13"/>
+    <col width="20.85546875" customWidth="1" min="14" max="14"/>
+    <col width="25.42578125" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Приложение 2 Сроки передачи ключей</t>
+          <t>Приложение 1 Сроки передачи ключей</t>
         </is>
       </c>
     </row>
@@ -612,8 +613,12 @@
 с переносом срока, ед.</t>
         </is>
       </c>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="8" t="n"/>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>из них:</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="n"/>
       <c r="O3" s="8" t="n"/>
     </row>
     <row r="4" ht="32.25" customHeight="1">
@@ -621,14 +626,18 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="13" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
-      <c r="L4" s="7" t="n"/>
-      <c r="M4" s="12" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Заключено ДС к ДДУ</t>
+        </is>
+      </c>
       <c r="N4" s="8" t="n"/>
       <c r="O4" s="5" t="inlineStr">
         <is>
@@ -641,7 +650,7 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
+      <c r="F5" s="10" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
@@ -653,7 +662,11 @@
           <t>количество ДС к ДДУ, ед.</t>
         </is>
       </c>
-      <c r="N5" s="12" t="n"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>дата передачи согласно ДС</t>
+        </is>
+      </c>
       <c r="O5" s="7" t="n"/>
     </row>
     <row r="6">
@@ -696,17 +709,17 @@
   <mergeCells count="13">
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:I5"/>
-    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="L3:L5"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="D3:D5"/>
     <mergeCell ref="G3:G5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="J3:J5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="46" fitToHeight="0"/>
